--- a/ig/main/ValueSet-1.2.250.1.213.1.1.5.655.xlsx
+++ b/ig/main/ValueSet-1.2.250.1.213.1.1.5.655.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="76">
   <si>
     <t>Property</t>
   </si>
@@ -78,19 +78,7 @@
     <t>Publisher</t>
   </si>
   <si>
-    <t>ANS</t>
-  </si>
-  <si>
-    <t>Contact</t>
-  </si>
-  <si>
-    <t>ANS (https://esante.gouv.fr)</t>
-  </si>
-  <si>
-    <t>Jurisdiction</t>
-  </si>
-  <si>
-    <t>France</t>
+    <t>Agence du Numérique en Santé (ANS) - 2-10 Rue d'Oradour-sur-Glane, 75015 Paris</t>
   </si>
   <si>
     <t>Description</t>
@@ -395,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -487,43 +475,27 @@
         <v>19</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>22</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="B12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="B13" t="s" s="2">
-        <v>9</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
-      </c>
-      <c r="B14" s="2"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="B15" s="2"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="s" s="2">
-        <v>26</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>27</v>
+        <v>22</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -542,42 +514,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -596,50 +568,50 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B6" t="s" s="2">
         <v>36</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -658,50 +630,50 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -720,34 +692,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s" s="2">
         <v>36</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -766,34 +738,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -812,34 +784,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s" s="2">
         <v>36</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -858,42 +830,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -912,42 +884,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -966,82 +938,82 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1060,34 +1032,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s" s="2">
         <v>36</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/ig/main/ValueSet-1.2.250.1.213.1.1.5.655.xlsx
+++ b/ig/main/ValueSet-1.2.250.1.213.1.1.5.655.xlsx
@@ -10,19 +10,12 @@
     <sheet name="Include #0" r:id="rId4" sheetId="2"/>
     <sheet name="Include #1" r:id="rId5" sheetId="3"/>
     <sheet name="Include #2" r:id="rId6" sheetId="4"/>
-    <sheet name="Include #3" r:id="rId7" sheetId="5"/>
-    <sheet name="Include #4" r:id="rId8" sheetId="6"/>
-    <sheet name="Include #5" r:id="rId9" sheetId="7"/>
-    <sheet name="Include #6" r:id="rId10" sheetId="8"/>
-    <sheet name="Include #7" r:id="rId11" sheetId="9"/>
-    <sheet name="Include #8" r:id="rId12" sheetId="10"/>
-    <sheet name="Include #9" r:id="rId13" sheetId="11"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="76">
   <si>
     <t>Property</t>
   </si>
@@ -72,13 +65,13 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-07-25T01:00:00+02:00</t>
+    <t>2023-07-25T00:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>Agence du Numérique en Santé (ANS) - 2-10 Rue d'Oradour-sur-Glane, 75015 Paris</t>
+    <t>Agence du Numérique en Santé(ANS) -2 - 10 Rue d'Oradour-sur-Glane, 75015 Paris</t>
   </si>
   <si>
     <t>Description</t>
@@ -99,6 +92,27 @@
     <t>Concept</t>
   </si>
   <si>
+    <t>C53610</t>
+  </si>
+  <si>
+    <t>Renouvellement</t>
+  </si>
+  <si>
+    <t>C43383</t>
+  </si>
+  <si>
+    <t>modèle</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>System URI</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/terminologie-ncit</t>
+  </si>
+  <si>
     <t>MED-897</t>
   </si>
   <si>
@@ -117,10 +131,76 @@
     <t>Date de fin d'adapation de la prescription</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>System URI</t>
+    <t>MED-1183</t>
+  </si>
+  <si>
+    <t>Produit d'entretien</t>
+  </si>
+  <si>
+    <t>MED-1180</t>
+  </si>
+  <si>
+    <t>Type de lentille</t>
+  </si>
+  <si>
+    <t>GEN-292</t>
+  </si>
+  <si>
+    <t>Commentaire</t>
+  </si>
+  <si>
+    <t>GEN-309</t>
+  </si>
+  <si>
+    <t>matériau</t>
+  </si>
+  <si>
+    <t>MED-1084</t>
+  </si>
+  <si>
+    <t>Diamètre lentille – lentille prescrite</t>
+  </si>
+  <si>
+    <t>MED-1085</t>
+  </si>
+  <si>
+    <t>Rayon 1 lentille – lentille prescrite</t>
+  </si>
+  <si>
+    <t>MED-1086</t>
+  </si>
+  <si>
+    <t>Rayon 2 lentille – lentille prescrite</t>
+  </si>
+  <si>
+    <t>GEN-092.08.04</t>
+  </si>
+  <si>
+    <t>Autre(s) paramètre(s)</t>
+  </si>
+  <si>
+    <t>MED-1065</t>
+  </si>
+  <si>
+    <t>Valeur de la kératométrie dans l'axe le plus plat</t>
+  </si>
+  <si>
+    <t>MED-1066</t>
+  </si>
+  <si>
+    <t>Valeur de la kératométrie dans l'axe le plus cambré</t>
+  </si>
+  <si>
+    <t>MED-1087</t>
+  </si>
+  <si>
+    <t>Puissance de la sphère – lentille prescrite</t>
+  </si>
+  <si>
+    <t>MED-1088</t>
+  </si>
+  <si>
+    <t>Puissance du cylindre – lentille prescrite</t>
   </si>
   <si>
     <t>https://smt.esante.gouv.fr/fhir/CodeSystem/1.2.250.1.213.1.1.4.322</t>
@@ -132,108 +212,18 @@
     <t>Date de fin de validité</t>
   </si>
   <si>
-    <t>urn:oid:2.16.840.1.113883.6.1</t>
-  </si>
-  <si>
-    <t>MED-1183</t>
-  </si>
-  <si>
-    <t>Produit d'entretien</t>
-  </si>
-  <si>
     <t>69730-0</t>
   </si>
   <si>
     <t>Consignes et conseils</t>
   </si>
   <si>
-    <t>MED-1180</t>
-  </si>
-  <si>
-    <t>Type de lentille</t>
-  </si>
-  <si>
-    <t>GEN-292</t>
-  </si>
-  <si>
-    <t>Commentaire</t>
-  </si>
-  <si>
-    <t>C53610</t>
-  </si>
-  <si>
-    <t>Renouvellement</t>
-  </si>
-  <si>
-    <t>C43383</t>
-  </si>
-  <si>
-    <t>modèle</t>
-  </si>
-  <si>
-    <t>urn:oid:2.16.840.1.113883.3.26.1.1</t>
-  </si>
-  <si>
-    <t>GEN-309</t>
-  </si>
-  <si>
-    <t>matériau</t>
-  </si>
-  <si>
-    <t>MED-1084</t>
-  </si>
-  <si>
-    <t>Diamètre lentille – lentille prescrite</t>
-  </si>
-  <si>
-    <t>MED-1085</t>
-  </si>
-  <si>
-    <t>Rayon 1 lentille – lentille prescrite</t>
-  </si>
-  <si>
-    <t>MED-1086</t>
-  </si>
-  <si>
-    <t>Rayon 2 lentille – lentille prescrite</t>
-  </si>
-  <si>
-    <t>GEN-092.08.04</t>
-  </si>
-  <si>
-    <t>Autre(s) paramètre(s)</t>
-  </si>
-  <si>
-    <t>MED-1065</t>
-  </si>
-  <si>
-    <t>Valeur de la kératométrie dans l'axe le plus plat</t>
-  </si>
-  <si>
-    <t>MED-1066</t>
-  </si>
-  <si>
-    <t>Valeur de la kératométrie dans l'axe le plus cambré</t>
-  </si>
-  <si>
     <t>95300-0</t>
   </si>
   <si>
     <t>Axe du K</t>
   </si>
   <si>
-    <t>MED-1087</t>
-  </si>
-  <si>
-    <t>Puissance de la sphère – lentille prescrite</t>
-  </si>
-  <si>
-    <t>MED-1088</t>
-  </si>
-  <si>
-    <t>Puissance du cylindre – lentille prescrite</t>
-  </si>
-  <si>
     <t>95325-7</t>
   </si>
   <si>
@@ -250,6 +240,9 @@
   </si>
   <si>
     <t>Addition – valeur</t>
+  </si>
+  <si>
+    <t>http://loinc.org</t>
   </si>
 </sst>
 </file>
@@ -503,7 +496,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
@@ -522,34 +515,34 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>66</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>67</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>69</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -557,9 +550,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -576,42 +569,138 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>71</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>73</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>74</v>
+        <v>36</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>75</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>31</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>36</v>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -619,9 +708,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -638,428 +727,66 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>25</v>
+        <v>63</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>26</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>28</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>29</v>
+        <v>67</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>30</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>31</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>32</v>
+        <v>71</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>33</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="30.703125" customWidth="true"/>
-    <col min="2" max="2" width="50.703125" customWidth="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>24</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>36</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="30.703125" customWidth="true"/>
-    <col min="2" max="2" width="50.703125" customWidth="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>24</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>33</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="30.703125" customWidth="true"/>
-    <col min="2" max="2" width="50.703125" customWidth="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>24</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>36</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="30.703125" customWidth="true"/>
-    <col min="2" max="2" width="50.703125" customWidth="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>24</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>41</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>43</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>33</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="30.703125" customWidth="true"/>
-    <col min="2" max="2" width="50.703125" customWidth="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>24</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>45</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>49</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="30.703125" customWidth="true"/>
-    <col min="2" max="2" width="50.703125" customWidth="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>24</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>50</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>52</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>54</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>56</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>59</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>61</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>62</v>
+        <v>29</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>63</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>33</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="30.703125" customWidth="true"/>
-    <col min="2" max="2" width="50.703125" customWidth="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>24</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>64</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>36</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>

--- a/ig/main/ValueSet-1.2.250.1.213.1.1.5.655.xlsx
+++ b/ig/main/ValueSet-1.2.250.1.213.1.1.5.655.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="78">
   <si>
     <t>Property</t>
   </si>
@@ -72,6 +72,12 @@
   </si>
   <si>
     <t>Agence du Numérique en Santé(ANS) -2 - 10 Rue d'Oradour-sur-Glane, 75015 Paris</t>
+  </si>
+  <si>
+    <t>Jurisdiction</t>
+  </si>
+  <si>
+    <t>France</t>
   </si>
   <si>
     <t>Description</t>
@@ -376,7 +382,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -468,27 +474,35 @@
         <v>19</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="B12" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>9</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="B14" t="s" s="2">
         <v>23</v>
+      </c>
+      <c r="B14" s="2"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -507,42 +521,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -561,146 +575,146 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -719,74 +733,74 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
